--- a/Philgeps_Monitoring_Summary.xlsx
+++ b/Philgeps_Monitoring_Summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\philgeps_monitorinh\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CE45E1-F45C-4842-BA91-C08CB051E0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8FD2C4-0DA3-45F9-8A19-51170610ED03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="June 26, 2026" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="47">
   <si>
     <t>Philgeps Monitoring</t>
   </si>
@@ -146,9 +146,6 @@
     <t>June 29, 2026 | 9:00 AM</t>
   </si>
   <si>
-    <t>Submmited online</t>
-  </si>
-  <si>
     <t>June 30, 2026 | 9:00 AM</t>
   </si>
   <si>
@@ -174,6 +171,12 @@
   </si>
   <si>
     <t>July 02, 2026 | 1:00 AM</t>
+  </si>
+  <si>
+    <t>For Canvas (in progress)</t>
+  </si>
+  <si>
+    <t>Submmited</t>
   </si>
 </sst>
 </file>
@@ -304,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -381,6 +384,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -710,7 +722,9 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="8">
+        <v>46199</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>4</v>
       </c>
@@ -838,7 +852,7 @@
         <v>21</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -889,7 +903,7 @@
         <v>25</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1095,7 +1109,7 @@
         <v>34</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1112,7 +1126,7 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14" s="27"/>
     </row>
@@ -1142,7 +1156,7 @@
         <v>34</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1159,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="27"/>
     </row>
@@ -1177,7 +1191,7 @@
         <v>13</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="28"/>
     </row>
@@ -1194,7 +1208,7 @@
         <v>34</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1211,7 +1225,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" s="27"/>
     </row>
@@ -1229,7 +1243,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C28" s="28"/>
     </row>
@@ -1253,70 +1267,59 @@
       <c r="B32" s="20"/>
       <c r="C32" s="22"/>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:4">
       <c r="A33" s="13"/>
       <c r="B33" s="14"/>
       <c r="C33" s="22"/>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="21">
-        <v>46202</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75">
-      <c r="A35" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" s="6"/>
-      <c r="C35" s="26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="7"/>
-      <c r="C36" s="27"/>
-    </row>
-    <row r="37" spans="1:3" ht="15.75">
-      <c r="A37" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B37" s="6"/>
-      <c r="C37" s="27"/>
-    </row>
-    <row r="38" spans="1:3" ht="15.75">
-      <c r="A38" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="27"/>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="28"/>
-    </row>
-    <row r="40" spans="1:3">
+      <c r="D33" s="20"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="15"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="20"/>
+    </row>
+    <row r="35" spans="1:4" ht="15.75">
+      <c r="A35" s="13"/>
+      <c r="B35" s="17"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="20"/>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="13"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="20"/>
+    </row>
+    <row r="37" spans="1:4" ht="15.75">
+      <c r="A37" s="13"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="20"/>
+    </row>
+    <row r="38" spans="1:4" ht="15.75">
+      <c r="A38" s="13"/>
+      <c r="B38" s="17"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="20"/>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="20"/>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="13"/>
       <c r="B40" s="14"/>
       <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="C24:C28"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C6:C10"/>
-    <mergeCell ref="C35:C39"/>
     <mergeCell ref="C12:C16"/>
     <mergeCell ref="C18:C22"/>
   </mergeCells>
@@ -1371,10 +1374,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="26" t="s">
         <v>41</v>
+      </c>
+      <c r="C6" s="29" t="s">
+        <v>45</v>
       </c>
       <c r="E6" s="13"/>
       <c r="F6" s="17"/>
@@ -1388,7 +1391,7 @@
       <c r="B7" s="7">
         <v>267500</v>
       </c>
-      <c r="C7" s="27"/>
+      <c r="C7" s="30"/>
       <c r="E7" s="13"/>
       <c r="F7" s="18"/>
       <c r="G7" s="22"/>
@@ -1399,9 +1402,9 @@
         <v>9</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="27"/>
+        <v>42</v>
+      </c>
+      <c r="C8" s="30"/>
       <c r="E8" s="13"/>
       <c r="F8" s="17"/>
       <c r="G8" s="22"/>
@@ -1412,9 +1415,9 @@
         <v>11</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="27"/>
+        <v>43</v>
+      </c>
+      <c r="C9" s="30"/>
       <c r="E9" s="13"/>
       <c r="F9" s="17"/>
       <c r="G9" s="22"/>
@@ -1425,9 +1428,9 @@
         <v>13</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="C10" s="31"/>
       <c r="E10" s="13"/>
       <c r="F10" s="14"/>
       <c r="G10" s="22"/>
@@ -1445,10 +1448,10 @@
         <v>5</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="26" t="s">
         <v>41</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1458,34 +1461,34 @@
       <c r="B13" s="7">
         <v>345500</v>
       </c>
-      <c r="C13" s="27"/>
+      <c r="C13" s="30"/>
     </row>
     <row r="14" spans="1:8" ht="15.75">
       <c r="A14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="27"/>
+        <v>42</v>
+      </c>
+      <c r="C14" s="30"/>
     </row>
     <row r="15" spans="1:8" ht="15.75">
       <c r="A15" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="27"/>
+        <v>43</v>
+      </c>
+      <c r="C15" s="30"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="28"/>
+        <v>44</v>
+      </c>
+      <c r="C16" s="31"/>
     </row>
     <row r="18" spans="1:3" ht="15.75">
       <c r="A18" s="5" t="s">
